--- a/config/lidar_calibration.xlsx
+++ b/config/lidar_calibration.xlsx
@@ -37,7 +37,7 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.10</v>
+        <v>0.25</v>
       </c>
       <c r="C2">
         <v>-15.00</v>

--- a/config/lidar_calibration.xlsx
+++ b/config/lidar_calibration.xlsx
@@ -113,7 +113,7 @@
         <v>-5.00</v>
       </c>
       <c r="D7">
-        <v>0.013</v>
+        <v>0.020</v>
       </c>
     </row>
   </sheetData>

--- a/config/lidar_calibration.xlsx
+++ b/config/lidar_calibration.xlsx
@@ -37,7 +37,7 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.10</v>
+        <v>0.18</v>
       </c>
       <c r="C2">
         <v>-15.00</v>
